--- a/Analysis/RAG_Ablation/rag_ablation_summary_by_decision_type.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_summary_by_decision_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,25 +495,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07247222222222223</v>
+        <v>0.08806190476190476</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09098621968237064</v>
+        <v>0.1025526927081471</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6264030627004673</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6778312163512967</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.8857142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1021527777777778</v>
+        <v>0.1178571428571428</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1123747329867151</v>
+        <v>0.1288665217659417</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.09264205630179587</v>
       </c>
       <c r="I3" t="n">
-        <v>0.125</v>
+        <v>0.09900074717013056</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="4">
@@ -581,25 +581,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03933333333333333</v>
+        <v>0.033975</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04450838410264186</v>
+        <v>0.03802286036317466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5666666666666668</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5">
@@ -624,25 +624,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09016666666666667</v>
+        <v>0.08417619047619049</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1005392630711499</v>
+        <v>0.0977666068723196</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.5333333333333332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9714285714285714</v>
       </c>
     </row>
     <row r="6">
@@ -667,25 +667,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1179444444444444</v>
+        <v>0.1215571428571428</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1272602035179114</v>
+        <v>0.1294257940236682</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06804138174397717</v>
+        <v>0.3435824282847902</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07216878364870323</v>
+        <v>0.3615949598252927</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -710,25 +710,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03609090909090909</v>
+        <v>0.03794166666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.037982721066308</v>
+        <v>0.04525146170344131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.657491495713053</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6933012701892219</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.85</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1824722222222222</v>
+        <v>0.1716714285714286</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1985582073143265</v>
+        <v>0.1933800647197901</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2749716523768433</v>
+        <v>0.1037998046244415</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3526709006307398</v>
+        <v>0.1352014516448251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="9">
@@ -796,25 +796,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1395833333333333</v>
+        <v>0.1237380952380952</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1542319846788872</v>
+        <v>0.136051224833181</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1075912199156613</v>
+        <v>0.0202020202020202</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1485431451105056</v>
+        <v>0.01515151515151516</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09436363636363637</v>
+        <v>0.07326666666666669</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1060987369907882</v>
+        <v>0.08280554462405793</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05754483289595019</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I10" t="n">
-        <v>0.112004618869898</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.45</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07277777777777779</v>
+        <v>0.08899523809523809</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08219202269890097</v>
+        <v>0.1009904577061634</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6513747150773105</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6555021169820366</v>
+        <v>0.4264705882352941</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="12">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1109583333333333</v>
+        <v>0.1161333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1188426401009421</v>
+        <v>0.1239733807340177</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1923778554045313</v>
+        <v>0.2279161638619205</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2361887464866651</v>
+        <v>0.2450037358506528</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="13">
@@ -968,25 +968,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03554545454545455</v>
+        <v>0.03455000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04076294976957374</v>
+        <v>0.0407469874498568</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.675</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="14">
@@ -1011,25 +1011,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1856111111111111</v>
+        <v>0.1512571428571428</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2032808591932725</v>
+        <v>0.174744087420311</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1916383190435099</v>
+        <v>0.02158863753791457</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1860042339640731</v>
+        <v>0.03046759955477193</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -1054,25 +1054,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1518194444444445</v>
+        <v>0.1262809523809524</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1608509065928707</v>
+        <v>0.1406082293318022</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3430130341208204</v>
+        <v>0.06718717951162087</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3415063509461096</v>
+        <v>0.05763405420141467</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6857142857142857</v>
       </c>
     </row>
     <row r="16">
@@ -1097,25 +1097,25 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09845454545454543</v>
+        <v>0.08445833333333332</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1092708209721416</v>
+        <v>0.09248812716888868</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.130692802504968</v>
       </c>
       <c r="I16" t="n">
-        <v>0.15</v>
+        <v>0.1508434423044442</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1096666666666666</v>
+        <v>0.1015904761904762</v>
       </c>
       <c r="G17" t="n">
-        <v>0.130859759472127</v>
+        <v>0.1202579612425957</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333332</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.3285714285714286</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="18">
@@ -1183,25 +1183,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1043333333333333</v>
+        <v>0.1259571428571428</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1117042877355834</v>
+        <v>0.1376442067126417</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2222222222222222</v>
+        <v>-0.08999514040745883</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2083333333333333</v>
+        <v>-0.1104578686795554</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K18" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>0.043</v>
+        <v>0.04328333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0517753642942208</v>
+        <v>0.049831405168644</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6802875679631266</v>
+        <v>0.3941921795275078</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7150932185258582</v>
+        <v>0.4200961894323341</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20">
@@ -1269,25 +1269,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06794444444444445</v>
+        <v>0.08652857142857144</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07752787287749725</v>
+        <v>0.1000252967581329</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7069302706328661</v>
+        <v>0.3714285714285715</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7805021169820366</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.8285714285714286</v>
       </c>
     </row>
     <row r="21">
@@ -1312,25 +1312,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1029861111111111</v>
+        <v>0.1114619047619047</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1091564581919534</v>
+        <v>0.1211408456444567</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4263463674541538</v>
+        <v>0.08184773753283857</v>
       </c>
       <c r="I21" t="n">
-        <v>0.424839684279443</v>
+        <v>0.09111988856921518</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K21" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="22">
@@ -1355,31 +1355,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0360757575757576</v>
+        <v>0.03262499999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04040517983850896</v>
+        <v>0.03655910287485593</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.775</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1398,31 +1398,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06052777777777779</v>
+        <v>0.131452380952381</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06631015748241524</v>
+        <v>0.1480451764135688</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7222222222222223</v>
+        <v>0.1757094261217446</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.1961721543938411</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.6857142857142857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09315277777777776</v>
+        <v>0.1392904761904762</v>
       </c>
       <c r="G24" t="n">
-        <v>0.115079335094653</v>
+        <v>0.1511941562175851</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01248582618842161</v>
+        <v>0.1790281806774544</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0111645496846301</v>
+        <v>0.1846886175753644</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1484,31 +1484,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>0.027</v>
+        <v>0.03341666666666669</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02979395762957346</v>
+        <v>0.03734821365985836</v>
       </c>
       <c r="H25" t="n">
-        <v>0.619681507357066</v>
+        <v>0.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6241841276167672</v>
+        <v>0.425</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.55</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1224904761904762</v>
       </c>
       <c r="G26" t="n">
-        <v>0.07632638023853382</v>
+        <v>0.1423971430069874</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7471938745990654</v>
+        <v>0.1238095238095238</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7693375672974065</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1570,31 +1570,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1094861111111111</v>
+        <v>0.1251857142857143</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1330418407096509</v>
+        <v>0.1433445551285816</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3180413817439772</v>
+        <v>0.1481000976877793</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3221687836487032</v>
+        <v>0.1323992741775875</v>
       </c>
       <c r="J27" t="n">
-        <v>0.25</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02980303030303031</v>
+        <v>0.03691666666666667</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0343140170598038</v>
+        <v>0.04422566770390803</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6196815073570661</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6241841276167672</v>
+        <v>0.375</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.55</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1656,31 +1656,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1874027777777778</v>
+        <v>0.2264809523809524</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2120819818047034</v>
+        <v>0.2595426287289534</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1111111111111111</v>
+        <v>-0.1376141880265065</v>
       </c>
       <c r="I29" t="n">
-        <v>0.125</v>
+        <v>-0.1533150115366983</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.75</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1699,31 +1699,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1784930555555555</v>
+        <v>0.1365285714285714</v>
       </c>
       <c r="G30" t="n">
-        <v>0.20618513728719</v>
+        <v>0.146552519861464</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.05555555555555556</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.08333333333333333</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K30" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1742,31 +1742,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0548939393939394</v>
+        <v>0.07432500000000002</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06096437465262017</v>
+        <v>0.08601720793146175</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.314982991426106</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3366025403784439</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.55</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07027777777777779</v>
+        <v>0.1271333333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07532119592396036</v>
+        <v>0.1474461305265957</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8027494301546209</v>
+        <v>0.1185665689788874</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8110042339640732</v>
+        <v>0.1247435829652697</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1828,31 +1828,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1147638888888889</v>
+        <v>0.1246047619047619</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1396479097128988</v>
+        <v>0.1415264360494113</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2777777777777777</v>
+        <v>0.04141399265094792</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2916666666666667</v>
+        <v>0.04565932032438047</v>
       </c>
       <c r="J33" t="n">
-        <v>0.25</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1871,31 +1871,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0286969696969697</v>
+        <v>0.03570000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03279672723591425</v>
+        <v>0.03981080318015901</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4106215229459643</v>
+        <v>0.5091751709536138</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4212704178377782</v>
+        <v>0.531698729810778</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1914,31 +1914,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1947916666666666</v>
+        <v>0.2307857142857143</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2223289001787211</v>
+        <v>0.2670010622111271</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-0.04761904761904762</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.04166666666666666</v>
+        <v>-0.05714285714285714</v>
       </c>
       <c r="J35" t="n">
-        <v>0.25</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K35" t="n">
-        <v>0.75</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1957,31 +1957,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1914305555555555</v>
+        <v>0.1445809523809524</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2095123182011898</v>
+        <v>0.1559593940152184</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1513747150773105</v>
+        <v>0.0857142857142857</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1555021169820366</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="J36" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2000,31 +2000,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05971212121212122</v>
+        <v>0.07849166666666668</v>
       </c>
       <c r="G37" t="n">
-        <v>0.06589703726893346</v>
+        <v>0.08819393764912233</v>
       </c>
       <c r="H37" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.03333333333333336</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.075</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.35</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2043,31 +2043,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08584722222222223</v>
+        <v>0.1480333333333334</v>
       </c>
       <c r="G38" t="n">
-        <v>0.09753485554868367</v>
+        <v>0.1780645370041337</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6513747150773105</v>
+        <v>0.1947570451693636</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6555021169820366</v>
+        <v>0.1818864401081268</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2086,31 +2086,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1299236111111111</v>
+        <v>0.1311571428571428</v>
       </c>
       <c r="G39" t="n">
-        <v>0.152023705474266</v>
+        <v>0.1463707607410168</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2560451437207024</v>
+        <v>0.07619047619047617</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.306002309434949</v>
+        <v>0.05714285714285713</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2129,31 +2129,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02914393939393938</v>
+        <v>0.04350833333333334</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03380848805259678</v>
+        <v>0.05203381981491358</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6363636363636362</v>
+        <v>0.5908248290463863</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.618301270189222</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2172,31 +2172,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F41" t="n">
-        <v>0.06969444444444445</v>
+        <v>0.121347619047619</v>
       </c>
       <c r="G41" t="n">
-        <v>0.07631652373961144</v>
+        <v>0.1383666212381113</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.07190962149730308</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.0895421313204446</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2215,31 +2215,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>0.08320833333333333</v>
+        <v>0.1219761904761905</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09638391324658019</v>
+        <v>0.1389085243686748</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2069302706328661</v>
+        <v>-0.01520108095310609</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2388354503153699</v>
+        <v>-0.01864631165339886</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2258,41 +2258,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02556060606060605</v>
+        <v>0.03153333333333336</v>
       </c>
       <c r="G43" t="n">
-        <v>0.03012650378725695</v>
+        <v>0.03767204747246579</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5757575757575757</v>
+        <v>0.4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2301,41 +2301,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1215694444444444</v>
+        <v>0.1023201058201058</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1428471980769549</v>
+        <v>0.1175780185197755</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.700743415417188e-17</v>
+        <v>0.03230229702535048</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.04166666666666666</v>
+        <v>0.05524841226347259</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2344,41 +2344,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1133888888888889</v>
+        <v>0.1268899470899471</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1297861892986815</v>
+        <v>0.1466455607497663</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.03451166054245663</v>
       </c>
       <c r="I45" t="n">
-        <v>0.375</v>
+        <v>-0.02614467169888848</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2387,41 +2387,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0405757575757576</v>
+        <v>0.05315185185185186</v>
       </c>
       <c r="G46" t="n">
-        <v>0.04782508622040245</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.3181818181818182</v>
-      </c>
+        <v>0.05919961174646284</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2430,41 +2426,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1189027777777778</v>
+        <v>0.1142761904761905</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1335698421746939</v>
+        <v>0.1292047122001037</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.4347889140034268</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.4587669473927447</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8285714285714286</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2473,41 +2469,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F48" t="n">
-        <v>0.09413888888888888</v>
+        <v>0.1281904761904762</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1118803700922648</v>
+        <v>0.1397831542068746</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1111111111111112</v>
+        <v>-0.1237116031708676</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.1615190005733998</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K48" t="n">
-        <v>0.75</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2516,41 +2512,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04434848484848488</v>
+        <v>0.04334166666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>0.05160594784009645</v>
+        <v>0.0528185549744282</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2559,41 +2555,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2147222222222222</v>
+        <v>0.1105142857142857</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2466496790693793</v>
+        <v>0.1310179285654805</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1348330225085812</v>
+        <v>0.3428571428571428</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1696386730713126</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="J50" t="n">
-        <v>0.25</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2602,41 +2598,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1474861111111111</v>
+        <v>0.1185142857142857</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1667859632223459</v>
+        <v>0.1353285128285635</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.4545454545454545</v>
+        <v>-0.08667638585174897</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5</v>
+        <v>-0.09336997692660348</v>
       </c>
       <c r="J51" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2645,41 +2641,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06001515151515151</v>
+        <v>0.057925</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07019586117223374</v>
+        <v>0.07379548462175201</v>
       </c>
       <c r="H52" t="n">
-        <v>0.393939393939394</v>
+        <v>0.242508504286947</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.231698729810778</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.55</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2688,41 +2684,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1198611111111111</v>
+        <v>0.1906952380952381</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1369810768927276</v>
+        <v>0.2123056571577677</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2939497021659964</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.326301490679731</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8857142857142857</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2731,41 +2727,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1094722222222222</v>
+        <v>0.1437047619047619</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1302477993740156</v>
+        <v>0.1614693076053759</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.05555555555555555</v>
+        <v>-0.1904761904761905</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.04166666666666666</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K54" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2774,41 +2770,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>0.04713636363636364</v>
+        <v>0.09457500000000002</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05239805435055795</v>
+        <v>0.1032870892066632</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.1657805218032136</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.1771592317781284</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.45</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2817,41 +2813,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>0.295375</v>
+        <v>0.1163904761904762</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3251577594189682</v>
+        <v>0.1336098256888353</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.293069729367134</v>
+        <v>0.3704664712911082</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3444978830179634</v>
+        <v>0.3780585945019679</v>
       </c>
       <c r="J56" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.8285714285714286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2860,41 +2856,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1408611111111111</v>
+        <v>0.1121047619047619</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1516953896869546</v>
+        <v>0.1285225688291021</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.1906812719880704</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>0.2019419236407188</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2903,41 +2899,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F58" t="n">
-        <v>0.07506060606060608</v>
+        <v>0.04459166666666665</v>
       </c>
       <c r="G58" t="n">
-        <v>0.09429480063023274</v>
+        <v>0.0523430708193386</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.2425085042869471</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.231698729810778</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.4</v>
       </c>
       <c r="K58" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2946,41 +2942,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1410833333333333</v>
+        <v>0.1821904761904762</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1641515133578943</v>
+        <v>0.1981828330073353</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2375141738115784</v>
+        <v>0.460461611698567</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3028312163512967</v>
+        <v>0.5028021774672377</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9714285714285714</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2989,41 +2985,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1144305555555556</v>
+        <v>0.1331142857142857</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1246888739724872</v>
+        <v>0.1533697682327652</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2777777777777777</v>
+        <v>0.1376141880265065</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.139029297250984</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3032,41 +3028,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03528787878787879</v>
+        <v>0.08143333333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>0.04152455929167029</v>
+        <v>0.09060268632471627</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2894094017338431</v>
+        <v>0.1894378766865388</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2849067814741419</v>
+        <v>0.2086369271125134</v>
       </c>
       <c r="J61" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.55</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3075,41 +3071,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1132361111111111</v>
+        <v>0.1027238095238095</v>
       </c>
       <c r="G62" t="n">
-        <v>0.132743315068553</v>
+        <v>0.1220799045882169</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.3566618070741255</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.339029297250984</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K62" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3118,41 +3114,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1100277777777778</v>
+        <v>0.1153571428571429</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1225577588368923</v>
+        <v>0.1316189751105765</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.260461611698567</v>
       </c>
       <c r="I63" t="n">
-        <v>0.375</v>
+        <v>0.2456593203243805</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3161,41 +3157,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0500909090909091</v>
+        <v>0.05409999999999998</v>
       </c>
       <c r="G64" t="n">
-        <v>0.05563637528523861</v>
+        <v>0.06358159688041196</v>
       </c>
       <c r="H64" t="n">
-        <v>0.316651204326763</v>
+        <v>0.2947010345812757</v>
       </c>
       <c r="I64" t="n">
-        <v>0.306002309434949</v>
+        <v>0.3139000850072503</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3204,41 +3200,41 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1139945987654321</v>
+        <v>0.0938904761904762</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1297105947656591</v>
+        <v>0.1092035556171556</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1954390831146418</v>
+        <v>0.3504567521060258</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2150932185258581</v>
+        <v>0.3989743318610787</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.8285714285714286</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3247,41 +3243,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1140933641975308</v>
+        <v>0.107947619047619</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1261172257992116</v>
+        <v>0.1203119226896358</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1145833333333334</v>
       </c>
       <c r="I66" t="n">
-        <v>0.15</v>
+        <v>0.125</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="K66" t="n">
-        <v>0.75</v>
+        <v>0.6857142857142857</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3290,924 +3286,25 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>0.056476430976431</v>
+        <v>0.04257499999999998</v>
       </c>
       <c r="G67" t="n">
-        <v>0.06251524214476802</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+        <v>0.04920707700632299</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.2224744871391589</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.2799038105676658</v>
+      </c>
       <c r="J67" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.55</v>
       </c>
       <c r="K67" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>alternate_embedding_k3</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>12</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.1152638888888889</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.1272351798763046</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>alternate_embedding_k3</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>12</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.117875</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.1382729756291113</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.1181508935020108</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.1574591643244434</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>alternate_embedding_k3</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>11</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.05095454545454547</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0.06409046511292944</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.04392393159949026</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.07872958216222171</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>control_k3</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Control k=3 standard</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>12</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.1054166666666667</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0.1256021554598329</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.5652352563430426</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.5915063509461097</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>control_k3</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Control k=3 standard</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>12</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.1283055555555555</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.1372769391347867</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.1212121212121212</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>control_k3</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Control k=3 standard</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>11</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.07257575757575757</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.09356729382325422</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.4333333333333334</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>descriptions_no_scores_ranks</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Descriptions without scores or ranks</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>12</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.1802777777777778</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.1980080509631048</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.6360827634879543</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.6860042339640732</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>descriptions_no_scores_ranks</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Descriptions without scores or ranks</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>12</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.1441388888888888</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.163724638841539</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-0.07728818961263097</v>
-      </c>
-      <c r="I75" t="n">
-        <v>-0.1030885996559601</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>descriptions_no_scores_ranks</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Descriptions without scores or ranks</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>11</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.09598484848484851</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.1039699300232459</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.3632993161855452</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.3732050807568877</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>exemplars_no_hidden_params</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Exemplars without hidden parameters</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>12</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.1250277777777778</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.1487465151526895</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>exemplars_no_hidden_params</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Exemplars without hidden parameters</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>12</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.127625</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.1520907140420056</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-0.1212121212121212</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-0.1363636363636364</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>exemplars_no_hidden_params</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Exemplars without hidden parameters</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>11</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.04712121212121211</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0.05741954298760483</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.3636363636363637</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>random_exemplars_k3</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>12</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.1688472222222222</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.1906400511307764</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.3583049857101765</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.3943375672974065</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>random_exemplars_k3</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>12</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.1593611111111111</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.1771379369265579</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.04166666666666666</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>random_exemplars_k3</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>11</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.0755909090909091</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.08506618689738515</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-0.2517762581901005</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-0.2182335127930839</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>retrieval_k1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>12</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.108375</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0.1169507243047466</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>retrieval_k1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>12</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.1344861111111111</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0.1601690198671435</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.293069729367134</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.38616454968463</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>retrieval_k1</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>11</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.06048484848484848</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0.06936849638232744</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.2483163247594393</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.2366025403784439</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Retrieval k=5</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Appliance</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>12</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.09208333333333331</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.1073318473289994</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.3735969372995327</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.36383545031537</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Retrieval k=5</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>HVAC</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>12</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.1341388888888888</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.154273172239671</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-0.2090599844111017</v>
-      </c>
-      <c r="I87" t="n">
-        <v>-0.2029137097789889</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>retrieval_k5</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Retrieval k=5</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Shower</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>11</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.04478787878787878</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0.05481327133878171</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.316651204326763</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0.306002309434949</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/RAG_Ablation/rag_ablation_summary_by_decision_type.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_summary_by_decision_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +547,7 @@
         <v>0.1288665217659417</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09264205630179587</v>
+        <v>0.09264205630179588</v>
       </c>
       <c r="I3" t="n">
         <v>0.09900074717013056</v>
@@ -630,7 +630,7 @@
         <v>0.08417619047619049</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0977666068723196</v>
+        <v>0.09776660687231958</v>
       </c>
       <c r="H5" t="n">
         <v>0.5333333333333332</v>
@@ -756,7 +756,7 @@
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1716714285714286</v>
+        <v>0.1716714285714285</v>
       </c>
       <c r="G8" t="n">
         <v>0.1933800647197901</v>
@@ -802,10 +802,10 @@
         <v>0.1237380952380952</v>
       </c>
       <c r="G9" t="n">
-        <v>0.136051224833181</v>
+        <v>0.1360512248331811</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0202020202020202</v>
+        <v>0.02020202020202022</v>
       </c>
       <c r="I9" t="n">
         <v>0.01515151515151516</v>
@@ -842,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07326666666666669</v>
+        <v>0.07326666666666667</v>
       </c>
       <c r="G10" t="n">
         <v>0.08280554462405793</v>
@@ -1063,7 +1063,7 @@
         <v>0.1406082293318022</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06718717951162087</v>
+        <v>0.06718717951162088</v>
       </c>
       <c r="I15" t="n">
         <v>0.05763405420141467</v>
@@ -1186,13 +1186,13 @@
         <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1259571428571428</v>
+        <v>0.1259571428571429</v>
       </c>
       <c r="G18" t="n">
         <v>0.1376442067126417</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.08999514040745883</v>
+        <v>-0.08999514040745885</v>
       </c>
       <c r="I18" t="n">
         <v>-0.1104578686795554</v>
@@ -1272,13 +1272,13 @@
         <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08652857142857144</v>
+        <v>0.08652857142857143</v>
       </c>
       <c r="G20" t="n">
         <v>0.1000252967581329</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3714285714285715</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="I20" t="n">
         <v>0.4</v>
@@ -1358,7 +1358,7 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>0.03262499999999999</v>
+        <v>0.032625</v>
       </c>
       <c r="G22" t="n">
         <v>0.03655910287485593</v>
@@ -1379,7 +1379,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1401,28 +1401,28 @@
         <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>0.131452380952381</v>
+        <v>0.06565238095238096</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1480451764135688</v>
+        <v>0.0750752712104989</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1757094261217446</v>
+        <v>0.6709475213598398</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1961721543938411</v>
+        <v>0.7104578686795554</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.9428571428571428</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1444,28 +1444,28 @@
         <v>35</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1392904761904762</v>
+        <v>0.1030333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1511941562175851</v>
+        <v>0.1135752970795146</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1790281806774544</v>
+        <v>0.2318901831271385</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1846886175753644</v>
+        <v>0.2885164631815233</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1487,19 +1487,19 @@
         <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03341666666666669</v>
+        <v>0.02489166666666668</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03734821365985836</v>
+        <v>0.02765141183452506</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4</v>
+        <v>0.7483163247594393</v>
       </c>
       <c r="I25" t="n">
-        <v>0.425</v>
+        <v>0.7616025403784439</v>
       </c>
       <c r="J25" t="n">
-        <v>0.55</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
         <v>0.9</v>
@@ -1508,7 +1508,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1530,28 +1530,28 @@
         <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1224904761904762</v>
+        <v>0.06530952380952382</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1423971430069874</v>
+        <v>0.07425275053678618</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1238095238095238</v>
+        <v>0.6847521855768224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.7209157373591109</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.9428571428571428</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1573,28 +1573,28 @@
         <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1251857142857143</v>
+        <v>0.09917619047619047</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1433445551285816</v>
+        <v>0.1128429907809411</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1481000976877793</v>
+        <v>0.0761904761904762</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1323992741775875</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6</v>
+        <v>0.6857142857142857</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1616,19 +1616,19 @@
         <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03691666666666667</v>
+        <v>0.02930000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.04422566770390803</v>
+        <v>0.03312037754344586</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.4091751709536137</v>
       </c>
       <c r="I28" t="n">
-        <v>0.375</v>
+        <v>0.4316987298107781</v>
       </c>
       <c r="J28" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
         <v>0.8</v>
@@ -1637,7 +1637,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1659,28 +1659,28 @@
         <v>35</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2264809523809524</v>
+        <v>0.1876904761904762</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2595426287289534</v>
+        <v>0.2141753944353819</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1376141880265065</v>
+        <v>0.180952380952381</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1533150115366983</v>
+        <v>0.1857142857142857</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1702,28 +1702,28 @@
         <v>35</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1365285714285714</v>
+        <v>0.1502238095238095</v>
       </c>
       <c r="G30" t="n">
-        <v>0.146552519861464</v>
+        <v>0.1694963195003815</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1142857142857143</v>
+        <v>0.1523809523809524</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1285714285714286</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1745,28 +1745,28 @@
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07432500000000002</v>
+        <v>0.05070000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08601720793146175</v>
+        <v>0.05693176395162112</v>
       </c>
       <c r="H31" t="n">
-        <v>0.314982991426106</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3366025403784439</v>
+        <v>0.375</v>
       </c>
       <c r="J31" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1788,28 +1788,28 @@
         <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1271333333333333</v>
+        <v>0.06711904761904763</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1474461305265957</v>
+        <v>0.07530411151079398</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1185665689788874</v>
+        <v>0.7090427594550779</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1247435829652697</v>
+        <v>0.7247435829652698</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1831,28 +1831,28 @@
         <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1246047619047619</v>
+        <v>0.1168333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1415264360494113</v>
+        <v>0.1355293470784099</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04141399265094792</v>
+        <v>0.147137997550316</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04565932032438047</v>
+        <v>0.1533150115366983</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.6857142857142857</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1874,16 +1874,16 @@
         <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03570000000000001</v>
+        <v>0.028825</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03981080318015901</v>
+        <v>0.03243345240598701</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5091751709536138</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="I34" t="n">
-        <v>0.531698729810778</v>
+        <v>0.475</v>
       </c>
       <c r="J34" t="n">
         <v>0.7</v>
@@ -1895,7 +1895,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1917,28 +1917,28 @@
         <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2307857142857143</v>
+        <v>0.1847952380952381</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2670010622111271</v>
+        <v>0.2108372227572335</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.04761904761904762</v>
+        <v>0.1757094261217446</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.05714285714285714</v>
+        <v>0.1676007258224126</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1960,19 +1960,19 @@
         <v>35</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1445809523809524</v>
+        <v>0.141647619047619</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1559593940152184</v>
+        <v>0.1575963761627669</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0857142857142857</v>
+        <v>0.01904761904761906</v>
       </c>
       <c r="I36" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K36" t="n">
         <v>0.7142857142857143</v>
@@ -1981,7 +1981,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2003,19 +2003,19 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07849166666666668</v>
+        <v>0.05470833333333334</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08819393764912233</v>
+        <v>0.05951331455463756</v>
       </c>
       <c r="H37" t="n">
-        <v>0.03333333333333336</v>
+        <v>0.457491495713053</v>
       </c>
       <c r="I37" t="n">
-        <v>0.075</v>
+        <v>0.468301270189222</v>
       </c>
       <c r="J37" t="n">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="K37" t="n">
         <v>0.75</v>
@@ -2024,7 +2024,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2046,28 +2046,28 @@
         <v>35</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1480333333333334</v>
+        <v>0.08930952380952381</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1780645370041337</v>
+        <v>0.1021934461049678</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1947570451693636</v>
+        <v>0.4604616116985669</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1818864401081268</v>
+        <v>0.474230748895809</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.8857142857142857</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2089,28 +2089,28 @@
         <v>35</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1311571428571428</v>
+        <v>0.1397095238095238</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1463707607410168</v>
+        <v>0.155090640998059</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07619047619047617</v>
+        <v>0.1861953357830173</v>
       </c>
       <c r="I39" t="n">
-        <v>0.05714285714285713</v>
+        <v>0.160970702749016</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2132,28 +2132,28 @@
         <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04350833333333334</v>
+        <v>0.03485833333333332</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05203381981491358</v>
+        <v>0.03927890664509805</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5908248290463863</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="I40" t="n">
-        <v>0.618301270189222</v>
+        <v>0.575</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="K40" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2175,28 +2175,28 @@
         <v>35</v>
       </c>
       <c r="F41" t="n">
-        <v>0.121347619047619</v>
+        <v>0.06620476190476192</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1383666212381113</v>
+        <v>0.07366839551221245</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07190962149730308</v>
+        <v>0.6233284737407921</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0895421313204446</v>
+        <v>0.6533150115366984</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2218,28 +2218,28 @@
         <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1219761904761905</v>
+        <v>0.09655714285714286</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1389085243686748</v>
+        <v>0.1090136609882905</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.01520108095310609</v>
+        <v>0.1376141880265065</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.01864631165339886</v>
+        <v>0.1247435829652697</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.4</v>
       </c>
       <c r="K42" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2261,38 +2261,38 @@
         <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>0.03153333333333336</v>
+        <v>0.02629166666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>0.03767204747246579</v>
+        <v>0.03020654854376574</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4</v>
+        <v>0.6091751709536137</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.6316987298107781</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2304,38 +2304,38 @@
         <v>35</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1023201058201058</v>
+        <v>0.131452380952381</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1175780185197755</v>
+        <v>0.1480451764135688</v>
       </c>
       <c r="H44" t="n">
-        <v>0.03230229702535048</v>
+        <v>0.1757094261217446</v>
       </c>
       <c r="I44" t="n">
-        <v>0.05524841226347259</v>
+        <v>0.1961721543938411</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6857142857142857</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2347,38 +2347,38 @@
         <v>35</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1268899470899471</v>
+        <v>0.1392904761904762</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1466455607497663</v>
+        <v>0.1511941562175851</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.03451166054245663</v>
+        <v>0.1790281806774544</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.02614467169888848</v>
+        <v>0.1846886175753644</v>
       </c>
       <c r="J45" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K45" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>alternate_embedding_k3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2390,34 +2390,38 @@
         <v>20</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05315185185185186</v>
+        <v>0.03341666666666669</v>
       </c>
       <c r="G46" t="n">
-        <v>0.05919961174646284</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+        <v>0.03734821365985836</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.425</v>
+      </c>
       <c r="J46" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2429,38 +2433,38 @@
         <v>35</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1142761904761905</v>
+        <v>0.1224904761904762</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1292047122001037</v>
+        <v>0.1423971430069874</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4347889140034268</v>
+        <v>0.1238095238095238</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4587669473927447</v>
+        <v>0.08571428571428572</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2472,38 +2476,38 @@
         <v>35</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1281904761904762</v>
+        <v>0.1251857142857143</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1397831542068746</v>
+        <v>0.1433445551285816</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1237116031708676</v>
+        <v>0.1481000976877793</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1615190005733998</v>
+        <v>0.1323992741775875</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2515,38 +2519,38 @@
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04334166666666667</v>
+        <v>0.03691666666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0528185549744282</v>
+        <v>0.04422566770390803</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="K49" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2558,38 +2562,38 @@
         <v>35</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1105142857142857</v>
+        <v>0.2264809523809524</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1310179285654805</v>
+        <v>0.2595426287289534</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3428571428571428</v>
+        <v>-0.1376141880265065</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3571428571428572</v>
+        <v>-0.1533150115366983</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.2</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2601,38 +2605,38 @@
         <v>35</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1185142857142857</v>
+        <v>0.1365285714285714</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1353285128285635</v>
+        <v>0.146552519861464</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.08667638585174897</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.09336997692660348</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2571428571428571</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
+          <t>Descriptions without scores or ranks</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2644,16 +2648,16 @@
         <v>20</v>
       </c>
       <c r="F52" t="n">
-        <v>0.057925</v>
+        <v>0.07432500000000002</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07379548462175201</v>
+        <v>0.08601720793146175</v>
       </c>
       <c r="H52" t="n">
-        <v>0.242508504286947</v>
+        <v>0.314982991426106</v>
       </c>
       <c r="I52" t="n">
-        <v>0.231698729810778</v>
+        <v>0.3366025403784439</v>
       </c>
       <c r="J52" t="n">
         <v>0.55</v>
@@ -2665,17 +2669,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2687,38 +2691,38 @@
         <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1906952380952381</v>
+        <v>0.1271333333333333</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2123056571577677</v>
+        <v>0.1474461305265957</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2939497021659964</v>
+        <v>0.1185665689788874</v>
       </c>
       <c r="I53" t="n">
-        <v>0.326301490679731</v>
+        <v>0.1247435829652697</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K53" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2730,38 +2734,38 @@
         <v>35</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1437047619047619</v>
+        <v>0.1246047619047619</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1614693076053759</v>
+        <v>0.1415264360494112</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1904761904761905</v>
+        <v>0.04141399265094795</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2142857142857143</v>
+        <v>0.04565932032438047</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>exemplars_no_hidden_params</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
+          <t>Exemplars without hidden parameters</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2773,38 +2777,38 @@
         <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>0.09457500000000002</v>
+        <v>0.03570000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1032870892066632</v>
+        <v>0.03981080318015901</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1657805218032136</v>
+        <v>0.5091751709536138</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1771592317781284</v>
+        <v>0.531698729810778</v>
       </c>
       <c r="J55" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="K55" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2816,38 +2820,38 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1163904761904762</v>
+        <v>0.2307857142857143</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1336098256888353</v>
+        <v>0.2670010622111271</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3704664712911082</v>
+        <v>-0.04761904761904764</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3780585945019679</v>
+        <v>-0.05714285714285714</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K56" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2859,38 +2863,38 @@
         <v>35</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1121047619047619</v>
+        <v>0.1445809523809524</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1285225688291021</v>
+        <v>0.1559593940152184</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1906812719880704</v>
+        <v>0.08571428571428567</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2019419236407188</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="J57" t="n">
         <v>0.4</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>random_exemplars_k3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
+          <t>Random exemplars k=3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2902,19 +2906,19 @@
         <v>20</v>
       </c>
       <c r="F58" t="n">
-        <v>0.04459166666666665</v>
+        <v>0.07849166666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0523430708193386</v>
+        <v>0.08819393764912233</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2425085042869471</v>
+        <v>0.03333333333333336</v>
       </c>
       <c r="I58" t="n">
-        <v>0.231698729810778</v>
+        <v>0.075</v>
       </c>
       <c r="J58" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K58" t="n">
         <v>0.75</v>
@@ -2923,17 +2927,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2945,38 +2949,38 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1821904761904762</v>
+        <v>0.1480333333333334</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1981828330073353</v>
+        <v>0.1780645370041337</v>
       </c>
       <c r="H59" t="n">
-        <v>0.460461611698567</v>
+        <v>0.1947570451693636</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5028021774672377</v>
+        <v>0.1818864401081268</v>
       </c>
       <c r="J59" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="K59" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.7714285714285715</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2988,38 +2992,38 @@
         <v>35</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1331142857142857</v>
+        <v>0.1311571428571428</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1533697682327652</v>
+        <v>0.1463707607410168</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1376141880265065</v>
+        <v>0.07619047619047617</v>
       </c>
       <c r="I60" t="n">
-        <v>0.139029297250984</v>
+        <v>0.05714285714285713</v>
       </c>
       <c r="J60" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>retrieval_k1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
+          <t>Retrieval k=1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3031,38 +3035,38 @@
         <v>20</v>
       </c>
       <c r="F61" t="n">
-        <v>0.08143333333333333</v>
+        <v>0.04350833333333334</v>
       </c>
       <c r="G61" t="n">
-        <v>0.09060268632471627</v>
+        <v>0.05203381981491358</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1894378766865388</v>
+        <v>0.5908248290463863</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2086369271125134</v>
+        <v>0.618301270189222</v>
       </c>
       <c r="J61" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="K61" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3074,38 +3078,38 @@
         <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1027238095238095</v>
+        <v>0.1213476190476191</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1220799045882169</v>
+        <v>0.1383666212381113</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3566618070741255</v>
+        <v>0.07190962149730309</v>
       </c>
       <c r="I62" t="n">
-        <v>0.339029297250984</v>
+        <v>0.0895421313204446</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3117,38 +3121,38 @@
         <v>35</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1153571428571429</v>
+        <v>0.1219761904761905</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1316189751105765</v>
+        <v>0.1389085243686748</v>
       </c>
       <c r="H63" t="n">
-        <v>0.260461611698567</v>
+        <v>-0.0152010809531061</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2456593203243805</v>
+        <v>-0.01864631165339886</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6285714285714286</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>retrieval_k5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
+          <t>Retrieval k=5</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3160,38 +3164,38 @@
         <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>0.05409999999999998</v>
+        <v>0.03153333333333336</v>
       </c>
       <c r="G64" t="n">
-        <v>0.06358159688041196</v>
+        <v>0.03767204747246579</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2947010345812757</v>
+        <v>0.4</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3139000850072503</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0.6</v>
       </c>
       <c r="K64" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3203,38 +3207,38 @@
         <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0938904761904762</v>
+        <v>0.1023201058201058</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1092035556171556</v>
+        <v>0.1175780185197755</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3504567521060258</v>
+        <v>0.03230229702535049</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3989743318610787</v>
+        <v>0.05524841226347259</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.4</v>
       </c>
       <c r="K65" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3246,38 +3250,38 @@
         <v>35</v>
       </c>
       <c r="F66" t="n">
-        <v>0.107947619047619</v>
+        <v>0.126889947089947</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1203119226896358</v>
+        <v>0.1466455607497663</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1145833333333334</v>
+        <v>-0.03451166054245662</v>
       </c>
       <c r="I66" t="n">
-        <v>0.125</v>
+        <v>-0.02614467169888848</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>nearest_neighbor_k3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
+          <t>Nearest-neighbor prediction k=3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3289,21 +3293,920 @@
         <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04257499999999998</v>
+        <v>0.05315185185185186</v>
       </c>
       <c r="G67" t="n">
-        <v>0.04920707700632299</v>
-      </c>
-      <c r="H67" t="n">
+        <v>0.05919961174646284</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>35</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.1142761904761905</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.1292047122001037</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.4347889140034268</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.4587669473927447</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>35</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.1281904761904762</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.1397831542068746</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.1237116031708676</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-0.1615190005733998</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.04334166666666667</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.05281855497442821</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>35</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.1105142857142857</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.1310179285654805</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.3428571428571428</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>35</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.1185142857142857</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1353285128285635</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.086676385851749</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-0.09336997692660348</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>20</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.057925</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.07379548462175201</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.242508504286947</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.231698729810778</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>35</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.1906952380952381</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.2123056571577677</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.2939497021659964</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.326301490679731</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>35</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.1437047619047619</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1614693076053759</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.1904761904761905</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-0.2142857142857143</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>20</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.09457500000000003</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1032870892066632</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.1657805218032136</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1771592317781284</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>35</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.1163904761904762</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1336098256888353</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.3704664712911082</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.3780585945019679</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>35</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.1121047619047619</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1285225688291021</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1906812719880704</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.2019419236407188</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>20</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.04459166666666665</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.05234307081933859</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.2425085042869471</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.231698729810778</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>35</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.1821904761904762</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1981828330073353</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.460461611698567</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.5028021774672377</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>35</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1331142857142857</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1533697682327652</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.1376141880265064</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.139029297250984</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>20</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.08143333333333333</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.09060268632471627</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.1894378766865388</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.2086369271125134</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>35</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.1027238095238095</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.1220799045882169</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.3566618070741255</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.339029297250984</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>35</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.1153571428571429</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.1316189751105765</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.260461611698567</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2456593203243805</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>20</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.06358159688041196</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.2947010345812757</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.3139000850072503</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>35</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.0938904761904762</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.1092035556171556</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.3504567521060258</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.3989743318610787</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>35</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.107947619047619</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.1203119226896358</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.1145833333333334</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>20</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.04257499999999999</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.049207077006323</v>
+      </c>
+      <c r="H88" t="n">
         <v>0.2224744871391589</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I88" t="n">
         <v>0.2799038105676658</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J88" t="n">
         <v>0.55</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K88" t="n">
         <v>0.8</v>
       </c>
     </row>
